--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,784 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125538341</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Olofstorp, Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>476033</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6504400</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stort antal utspridda i sluttningen, flertal torkade blomstänglar från i fjol. Barrnaturskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125538448</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Olofstorp, Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476083</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6504419</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohål i äldre tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125536906</v>
+      </c>
+      <c r="B6" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Olofstorp, Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476032</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6504355</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Barrnaturskog, senvuxen 150 år+</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125538852</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Olofstorp, Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>476162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6504432</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125537917</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96897</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Olofstorp, Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476033</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6504400</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125537373</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Olofstorp, Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>476029</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6504350</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Barrnaturskog, ålder 150 år+</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,10 +1453,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125537917</v>
+        <v>125537373</v>
       </c>
       <c r="B8" t="n">
-        <v>96897</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1465,38 +1465,57 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476033</v>
+        <v>476029</v>
       </c>
       <c r="R8" t="n">
-        <v>6504400</v>
+        <v>6504350</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1528,7 +1547,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1538,7 +1557,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Barrnaturskog, ålder 150 år+</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1562,142 +1586,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>125537373</v>
-      </c>
-      <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Olofstorp, Olofstorp, Vg</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>476029</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6504350</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Karlsborg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Undenäs</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Barrnaturskog, ålder 150 år+</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Boel Nilsson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Boel Nilsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125538341</v>
+        <v>125538448</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,40 +935,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -982,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476033</v>
+        <v>476083</v>
       </c>
       <c r="R4" t="n">
-        <v>6504400</v>
+        <v>6504419</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,12 +1022,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Stort antal utspridda i sluttningen, flertal torkade blomstänglar från i fjol. Barrnaturskog.</t>
+          <t>Bohål i äldre tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125538448</v>
+        <v>125538341</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,35 +1066,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476083</v>
+        <v>476033</v>
       </c>
       <c r="R5" t="n">
-        <v>6504419</v>
+        <v>6504400</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bohål i äldre tall</t>
+          <t>Stort antal utspridda i sluttningen, flertal torkade blomstänglar från i fjol. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125536906</v>
+        <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>74964</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,38 +1202,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476032</v>
+        <v>476029</v>
       </c>
       <c r="R6" t="n">
-        <v>6504355</v>
+        <v>6504350</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1265,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1275,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Barrnaturskog, senvuxen 150 år+</t>
+          <t>Barrnaturskog, ålder 150 år+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,21 +1310,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1322,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125538852</v>
+        <v>125536906</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>74964</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,52 +1338,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476162</v>
+        <v>476032</v>
       </c>
       <c r="R7" t="n">
-        <v>6504432</v>
+        <v>6504355</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1411,7 +1401,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1421,12 +1411,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
+          <t>Barrnaturskog, senvuxen 150 år+</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,6 +1427,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1453,10 +1458,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125537373</v>
+        <v>125538852</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1465,40 +1470,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476029</v>
+        <v>476162</v>
       </c>
       <c r="R8" t="n">
-        <v>6504350</v>
+        <v>6504432</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Barrnaturskog, ålder 150 år+</t>
+          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -923,64 +923,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125538448</v>
+        <v>125536906</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476083</v>
+        <v>476032</v>
       </c>
       <c r="R4" t="n">
-        <v>6504419</v>
+        <v>6504355</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1012,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål i äldre tall</t>
+          <t>Barrnaturskog, senvuxen 150 år+</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,6 +1019,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1054,52 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125538341</v>
+        <v>125538852</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1113,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476033</v>
+        <v>476162</v>
       </c>
       <c r="R5" t="n">
-        <v>6504400</v>
+        <v>6504432</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1148,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,12 +1144,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Stort antal utspridda i sluttningen, flertal torkade blomstänglar från i fjol. Barrnaturskog.</t>
+          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,15 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125537373</v>
+        <v>125537690</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1206,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1249,10 +1230,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476029</v>
+        <v>476033</v>
       </c>
       <c r="R6" t="n">
-        <v>6504350</v>
+        <v>6504400</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1284,7 +1265,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1275,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Barrnaturskog, ålder 150 år+</t>
+          <t>Barrnaturskog, senvuxen. Ålder 150 år+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,50 +1307,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125536906</v>
+        <v>125538448</v>
       </c>
       <c r="B7" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476032</v>
+        <v>476083</v>
       </c>
       <c r="R7" t="n">
-        <v>6504355</v>
+        <v>6504419</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1401,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1401,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Barrnaturskog, senvuxen 150 år+</t>
+          <t>Bohål i äldre tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,21 +1417,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1458,47 +1433,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125538852</v>
+        <v>125537373</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1512,10 +1487,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476162</v>
+        <v>476029</v>
       </c>
       <c r="R8" t="n">
-        <v>6504432</v>
+        <v>6504350</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1547,7 +1522,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1557,12 +1532,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
+          <t>Barrnaturskog, ålder 150 år+</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>125537690</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>125537373</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>125536906</v>
       </c>
       <c r="B4" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>125537690</v>
       </c>
       <c r="B6" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>125537373</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>125537690</v>
       </c>
       <c r="B6" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>125537373</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>125537690</v>
       </c>
       <c r="B6" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>125537373</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>125536906</v>
       </c>
       <c r="B4" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>125538852</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>125537690</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>125538448</v>
       </c>
       <c r="B7" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>125537373</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20830-2025 artfynd.xlsx
+++ b/artfynd/A 20830-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>125537690</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>125537373</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
